--- a/output7/【河洛文讀注音-閩拼調符】《知否，知否？應是綠肥紅瘦》.xlsx
+++ b/output7/【河洛文讀注音-閩拼調符】《知否，知否？應是綠肥紅瘦》.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E90873FC-DE07-42FC-A8E4-D39A6F58C1F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4DC18A-4AA4-4ACC-96DD-1F1914AEC483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="181">
   <si>
     <t>Key</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -158,6 +158,9 @@
     <t>N/A</t>
   </si>
   <si>
+    <t>(5, 5)</t>
+  </si>
+  <si>
     <t>網頁每列字數</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -227,6 +230,18 @@
   </si>
   <si>
     <t>wǔ</t>
+  </si>
+  <si>
+    <t>漢字</t>
+  </si>
+  <si>
+    <t>台語音標</t>
+  </si>
+  <si>
+    <t>校正音標</t>
+  </si>
+  <si>
+    <t>座標</t>
   </si>
   <si>
     <t>知</t>
@@ -331,9 +346,6 @@
   </si>
   <si>
     <t>ti1</t>
-  </si>
-  <si>
-    <t>dī</t>
   </si>
   <si>
     <t>ing1</t>
@@ -619,6 +631,17 @@
   </si>
   <si>
     <t>知否？知否？.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zai1</t>
+  </si>
+  <si>
+    <t>zai1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zāi</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1638,7 +1661,7 @@
     </row>
     <row r="2" spans="2:4" ht="30">
       <c r="B2" s="37" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="40">
         <v>1</v>
@@ -1646,10 +1669,10 @@
     </row>
     <row r="3" spans="2:4" ht="30">
       <c r="B3" s="37" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="2:4">
@@ -1663,7 +1686,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="2:4">
@@ -1671,7 +1694,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="2:4">
@@ -1679,7 +1702,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D7" s="44"/>
     </row>
@@ -1688,7 +1711,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="30">
@@ -1730,7 +1753,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="30">
@@ -1738,7 +1761,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="30">
@@ -1746,7 +1769,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="30">
@@ -1754,7 +1777,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="30">
@@ -1762,7 +1785,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="30">
@@ -1770,7 +1793,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="30">
@@ -1778,12 +1801,12 @@
         <v>17</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="30">
       <c r="B20" s="37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20" s="43">
         <v>0</v>
@@ -1822,16 +1845,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1842,441 +1865,455 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57416C5C-3BC9-4172-97A7-CE008297FA68}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C1" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D1" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="C3" t="s">
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="C4" t="s">
         <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
         <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>159</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="C9" t="s">
         <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s">
         <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
         <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
         <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C15" t="s">
         <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B16" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
         <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
         <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C18" t="s">
         <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C19" t="s">
         <v>26</v>
       </c>
       <c r="D19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C20" t="s">
         <v>26</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B21" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C21" t="s">
         <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B22" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C22" t="s">
         <v>26</v>
       </c>
       <c r="D22" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B23" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="C23" t="s">
         <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B24" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
       <c r="C24" t="s">
         <v>26</v>
       </c>
       <c r="D24" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="C25" t="s">
         <v>26</v>
       </c>
       <c r="D25" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>128</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
         <v>26</v>
       </c>
       <c r="D26" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B27" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C27" t="s">
         <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B28" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C28" t="s">
         <v>26</v>
       </c>
       <c r="D28" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B29" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C29" t="s">
         <v>26</v>
       </c>
       <c r="D29" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C30" t="s">
         <v>26</v>
       </c>
       <c r="D30" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C31" t="s">
         <v>26</v>
       </c>
       <c r="D31" t="s">
-        <v>150</v>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32" t="s">
+        <v>142</v>
+      </c>
+      <c r="C32" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2287,63 +2324,77 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF1EEEE7-2560-4025-ACE8-AC4D4EB27C23}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C1" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D1" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C3" t="s">
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
         <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2469,9 +2520,11 @@
       <c r="B3" s="12"/>
       <c r="C3" s="13"/>
       <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
+      <c r="E3" s="48" t="s">
+        <v>179</v>
+      </c>
       <c r="F3" s="48" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G3" s="48"/>
       <c r="H3" s="48"/>
@@ -2482,52 +2535,52 @@
       <c r="M3" s="48"/>
       <c r="N3" s="48"/>
       <c r="O3" s="48" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="P3" s="48" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="Q3" s="48"/>
       <c r="R3" s="48"/>
       <c r="T3" s="15"/>
       <c r="V3" s="51" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B4" s="16"/>
       <c r="D4" s="55"/>
       <c r="E4" s="55" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="F4" s="55" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G4" s="55"/>
       <c r="H4" s="55" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="I4" s="55" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J4" s="55"/>
       <c r="K4" s="55" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L4" s="55" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="M4" s="55" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="N4" s="55" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="O4" s="55" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="P4" s="55" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="Q4" s="55"/>
       <c r="R4" s="55"/>
@@ -2539,46 +2592,46 @@
         <v>1</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5" s="54" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F5" s="54" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G5" s="54" t="s">
         <v>18</v>
       </c>
       <c r="H5" s="54" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I5" s="54" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="J5" s="54" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K5" s="54" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="L5" s="54" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="M5" s="54" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="N5" s="54" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="O5" s="54" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="P5" s="54" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Q5" s="54" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R5" s="54" t="str">
         <f>CHAR(10)</f>
@@ -2593,36 +2646,36 @@
       <c r="C6" s="21"/>
       <c r="D6" s="56"/>
       <c r="E6" s="56" t="s">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="F6" s="56" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G6" s="56"/>
       <c r="H6" s="56" t="s">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="I6" s="56" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="J6" s="56"/>
       <c r="K6" s="56" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="L6" s="56" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="M6" s="56" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="N6" s="56" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="O6" s="56" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="P6" s="56" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="Q6" s="56"/>
       <c r="R6" s="56"/>
@@ -2653,41 +2706,41 @@
     <row r="8" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="16"/>
       <c r="D8" s="55" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E8" s="55" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F8" s="55" t="s">
         <v>24</v>
       </c>
       <c r="G8" s="55" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H8" s="55" t="s">
         <v>25</v>
       </c>
       <c r="I8" s="55" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="J8" s="55"/>
       <c r="K8" s="55" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="L8" s="55" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="M8" s="55" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="N8" s="55" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="O8" s="55" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="P8" s="55" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="Q8" s="55"/>
       <c r="R8" s="55"/>
@@ -2700,43 +2753,43 @@
         <v>2</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E9" s="54" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G9" s="54" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H9" s="54" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="54" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J9" s="54" t="s">
         <v>18</v>
       </c>
       <c r="K9" s="54" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="L9" s="54" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M9" s="54" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="N9" s="54" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="O9" s="54" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="P9" s="54" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Q9" s="54" t="s">
         <v>19</v>
@@ -2753,41 +2806,41 @@
     <row r="10" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="20"/>
       <c r="D10" s="56" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E10" s="56" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F10" s="56" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G10" s="56" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H10" s="56" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I10" s="56" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J10" s="56"/>
       <c r="K10" s="56" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="L10" s="56" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M10" s="56" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="N10" s="56" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="O10" s="56" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="P10" s="56" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="Q10" s="56"/>
       <c r="R10" s="56"/>
@@ -2817,38 +2870,38 @@
     <row r="12" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="16"/>
       <c r="D12" s="55" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E12" s="55" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F12" s="55" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G12" s="55" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H12" s="55" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="55"/>
       <c r="J12" s="55" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K12" s="55" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="L12" s="55" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="M12" s="55" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="N12" s="55" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="O12" s="55" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="P12" s="55"/>
       <c r="Q12" s="55"/>
@@ -2862,16 +2915,16 @@
         <v>3</v>
       </c>
       <c r="D13" s="54" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E13" s="54" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F13" s="54" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G13" s="54" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H13" s="54" t="s">
         <v>20</v>
@@ -2880,22 +2933,22 @@
         <v>18</v>
       </c>
       <c r="J13" s="54" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K13" s="54" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="L13" s="54" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="M13" s="54" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N13" s="54" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O13" s="54" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="P13" s="54" t="s">
         <v>19</v>
@@ -2912,38 +2965,38 @@
     <row r="14" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="20"/>
       <c r="D14" s="56" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E14" s="56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F14" s="56" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G14" s="56" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H14" s="56" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I14" s="56"/>
       <c r="J14" s="56" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K14" s="56" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="L14" s="56" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="M14" s="56" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="N14" s="56" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="O14" s="56" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="P14" s="56"/>
       <c r="Q14" s="56"/>
@@ -2974,36 +3027,36 @@
     <row r="16" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="16"/>
       <c r="D16" s="55" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="E16" s="55" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F16" s="55"/>
       <c r="G16" s="55" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="H16" s="55" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="I16" s="55"/>
       <c r="J16" s="55" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K16" s="55" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L16" s="55" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="M16" s="55" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="N16" s="55" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="O16" s="55" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="P16" s="55"/>
       <c r="Q16" s="55"/>
@@ -3017,40 +3070,40 @@
         <v>4</v>
       </c>
       <c r="D17" s="54" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E17" s="54" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F17" s="54" t="s">
         <v>18</v>
       </c>
       <c r="G17" s="54" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H17" s="54" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="I17" s="54" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J17" s="54" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="K17" s="54" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="L17" s="54" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="M17" s="54" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="N17" s="54" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O17" s="54" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="P17" s="54" t="s">
         <v>19</v>
@@ -3067,36 +3120,36 @@
     <row r="18" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="20"/>
       <c r="D18" s="56" t="s">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="E18" s="56" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F18" s="56"/>
       <c r="G18" s="56" t="s">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="H18" s="56" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I18" s="56"/>
       <c r="J18" s="56" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K18" s="56" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="L18" s="56" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="M18" s="56" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="N18" s="56" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="O18" s="56" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="P18" s="56"/>
       <c r="Q18" s="56"/>

--- a/output7/【河洛文讀注音-閩拼調符】《知否，知否？應是綠肥紅瘦》.xlsx
+++ b/output7/【河洛文讀注音-閩拼調符】《知否，知否？應是綠肥紅瘦》.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4DC18A-4AA4-4ACC-96DD-1F1914AEC483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC434253-D50E-4EF4-9790-1A02D3CE835B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="180">
   <si>
     <t>Key</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -343,9 +343,6 @@
   <si>
     <t>知否，知否？應是綠肥紅瘦</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ti1</t>
   </si>
   <si>
     <t>ing1</t>
@@ -1686,7 +1683,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="2:4">
@@ -1702,7 +1699,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D7" s="44"/>
     </row>
@@ -1865,7 +1862,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57416C5C-3BC9-4172-97A7-CE008297FA68}">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1887,49 +1884,49 @@
         <v>53</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>177</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="C3" t="s">
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
         <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
         <v>26</v>
@@ -1940,10 +1937,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
         <v>26</v>
@@ -1954,10 +1951,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
@@ -1968,38 +1965,38 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>162</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>163</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
         <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>176</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
@@ -2010,10 +2007,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B11" t="s">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
         <v>26</v>
@@ -2024,10 +2021,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
@@ -2038,10 +2035,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
         <v>26</v>
@@ -2052,10 +2049,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
         <v>26</v>
@@ -2066,38 +2063,38 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s">
         <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
         <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C17" t="s">
         <v>26</v>
@@ -2108,10 +2105,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C18" t="s">
         <v>26</v>
@@ -2122,10 +2119,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
         <v>26</v>
@@ -2136,10 +2133,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C20" t="s">
         <v>26</v>
@@ -2150,24 +2147,24 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="C21" t="s">
         <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C22" t="s">
         <v>26</v>
@@ -2178,10 +2175,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B23" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="C23" t="s">
         <v>26</v>
@@ -2192,10 +2189,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B24" t="s">
-        <v>167</v>
+        <v>129</v>
       </c>
       <c r="C24" t="s">
         <v>26</v>
@@ -2206,10 +2203,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="B25" t="s">
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
         <v>26</v>
@@ -2220,10 +2217,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>131</v>
       </c>
       <c r="C26" t="s">
         <v>26</v>
@@ -2234,10 +2231,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B27" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C27" t="s">
         <v>26</v>
@@ -2248,10 +2245,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B28" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C28" t="s">
         <v>26</v>
@@ -2262,10 +2259,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C29" t="s">
         <v>26</v>
@@ -2276,10 +2273,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C30" t="s">
         <v>26</v>
@@ -2290,30 +2287,16 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B31" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C31" t="s">
         <v>26</v>
       </c>
       <c r="D31" t="s">
         <v>153</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" t="s">
-        <v>82</v>
-      </c>
-      <c r="B32" t="s">
-        <v>142</v>
-      </c>
-      <c r="C32" t="s">
-        <v>26</v>
-      </c>
-      <c r="D32" t="s">
-        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2346,13 +2329,13 @@
         <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2360,13 +2343,13 @@
         <v>54</v>
       </c>
       <c r="B3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C3" t="s">
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2374,13 +2357,13 @@
         <v>61</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C4" t="s">
         <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2388,7 +2371,7 @@
         <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C5" t="s">
         <v>26</v>
@@ -2521,10 +2504,10 @@
       <c r="C3" s="13"/>
       <c r="D3" s="48"/>
       <c r="E3" s="48" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F3" s="48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G3" s="48"/>
       <c r="H3" s="48"/>
@@ -2535,10 +2518,10 @@
       <c r="M3" s="48"/>
       <c r="N3" s="48"/>
       <c r="O3" s="48" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P3" s="48" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q3" s="48"/>
       <c r="R3" s="48"/>
@@ -2551,36 +2534,36 @@
       <c r="B4" s="16"/>
       <c r="D4" s="55"/>
       <c r="E4" s="55" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F4" s="55" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G4" s="55"/>
       <c r="H4" s="55" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I4" s="55" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J4" s="55"/>
       <c r="K4" s="55" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L4" s="55" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M4" s="55" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N4" s="55" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O4" s="55" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P4" s="55" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q4" s="55"/>
       <c r="R4" s="55"/>
@@ -2646,36 +2629,36 @@
       <c r="C6" s="21"/>
       <c r="D6" s="56"/>
       <c r="E6" s="56" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F6" s="56" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G6" s="56"/>
       <c r="H6" s="56" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I6" s="56" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J6" s="56"/>
       <c r="K6" s="56" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L6" s="56" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M6" s="56" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N6" s="56" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O6" s="56" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P6" s="56" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q6" s="56"/>
       <c r="R6" s="56"/>
@@ -2706,41 +2689,41 @@
     <row r="8" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="16"/>
       <c r="D8" s="55" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E8" s="55" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F8" s="55" t="s">
         <v>24</v>
       </c>
       <c r="G8" s="55" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H8" s="55" t="s">
         <v>25</v>
       </c>
       <c r="I8" s="55" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J8" s="55"/>
       <c r="K8" s="55" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L8" s="55" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M8" s="55" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N8" s="55" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O8" s="55" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P8" s="55" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q8" s="55"/>
       <c r="R8" s="55"/>
@@ -2806,41 +2789,41 @@
     <row r="10" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="20"/>
       <c r="D10" s="56" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E10" s="56" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F10" s="56" t="s">
         <v>48</v>
       </c>
       <c r="G10" s="56" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H10" s="56" t="s">
         <v>46</v>
       </c>
       <c r="I10" s="56" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J10" s="56"/>
       <c r="K10" s="56" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L10" s="56" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M10" s="56" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N10" s="56" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O10" s="56" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P10" s="56" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q10" s="56"/>
       <c r="R10" s="56"/>
@@ -2870,38 +2853,38 @@
     <row r="12" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="16"/>
       <c r="D12" s="55" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E12" s="55" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F12" s="55" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G12" s="55" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H12" s="55" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="55"/>
       <c r="J12" s="55" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K12" s="55" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L12" s="55" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M12" s="55" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N12" s="55" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O12" s="55" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P12" s="55"/>
       <c r="Q12" s="55"/>
@@ -2965,38 +2948,38 @@
     <row r="14" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="20"/>
       <c r="D14" s="56" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E14" s="56" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F14" s="56" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G14" s="56" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H14" s="56" t="s">
         <v>47</v>
       </c>
       <c r="I14" s="56"/>
       <c r="J14" s="56" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K14" s="56" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L14" s="56" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M14" s="56" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N14" s="56" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O14" s="56" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P14" s="56"/>
       <c r="Q14" s="56"/>
@@ -3027,36 +3010,36 @@
     <row r="16" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="16"/>
       <c r="D16" s="55" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E16" s="55" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F16" s="55"/>
       <c r="G16" s="55" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H16" s="55" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I16" s="55"/>
       <c r="J16" s="55" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K16" s="55" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L16" s="55" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M16" s="55" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N16" s="55" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O16" s="55" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P16" s="55"/>
       <c r="Q16" s="55"/>
@@ -3120,36 +3103,36 @@
     <row r="18" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="20"/>
       <c r="D18" s="56" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E18" s="56" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F18" s="56"/>
       <c r="G18" s="56" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H18" s="56" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I18" s="56"/>
       <c r="J18" s="56" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K18" s="56" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L18" s="56" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M18" s="56" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N18" s="56" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O18" s="56" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P18" s="56"/>
       <c r="Q18" s="56"/>

--- a/output7/【河洛文讀注音-閩拼調符】《知否，知否？應是綠肥紅瘦》.xlsx
+++ b/output7/【河洛文讀注音-閩拼調符】《知否，知否？應是綠肥紅瘦》.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC434253-D50E-4EF4-9790-1A02D3CE835B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB696AE-1182-4684-9D66-1B36AF0B980A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
